--- a/experiment3/data_processing/exp_data/08_ranova_input.xlsx
+++ b/experiment3/data_processing/exp_data/08_ranova_input.xlsx
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>770.2692307692307</v>
+        <v>768.5833333333334</v>
       </c>
     </row>
     <row r="60">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>448.5625</v>
+        <v>449.0333333333334</v>
       </c>
     </row>
     <row r="74">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>413.4285714285714</v>
+        <v>405.4444444444445</v>
       </c>
     </row>
     <row r="86">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>690.64</v>
+        <v>643.5909090909091</v>
       </c>
     </row>
     <row r="146">
@@ -6003,7 +6003,7 @@
         <v>683.6190476190476</v>
       </c>
       <c r="E11" t="n">
-        <v>770.2692307692307</v>
+        <v>768.5833333333334</v>
       </c>
       <c r="F11" t="n">
         <v>663.4090909090909</v>
@@ -6055,7 +6055,7 @@
         <v>541.9285714285714</v>
       </c>
       <c r="G13" t="n">
-        <v>448.5625</v>
+        <v>449.0333333333334</v>
       </c>
     </row>
     <row r="14">
@@ -6101,7 +6101,7 @@
         <v>454.0384615384615</v>
       </c>
       <c r="G15" t="n">
-        <v>413.4285714285714</v>
+        <v>405.4444444444445</v>
       </c>
     </row>
     <row r="16">
@@ -6331,7 +6331,7 @@
         <v>657.2083333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>690.64</v>
+        <v>643.5909090909091</v>
       </c>
     </row>
     <row r="26">
